--- a/release_1_0_0/data/files/input/rod_pilot_concepts_flat.xlsx
+++ b/release_1_0_0/data/files/input/rod_pilot_concepts_flat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,10 +429,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>partenaire</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
@@ -451,10 +456,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Adixon</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>IBB NICE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ibis budget Nice</t>
         </is>
@@ -468,15 +478,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Selfly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>IBB STRA</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Ibis budget Strasbourg Centre République</t>
         </is>
@@ -485,66 +500,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H6188</t>
+          <t>H0373</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIBERTY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MER BOUL</t>
+          <t>Selfly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mercure Paris Boulogne</t>
+          <t>MER MONT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mercure Paris Montmartre Sacré-Cœur</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>H1249</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIBERTY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NOV MEG</t>
+          <t>Boost</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Novotel Megève Mont-Blanc</t>
+          <t>MER RENNES</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mercure Rennes Centre Gare</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H0373</t>
+          <t>HB5I0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONNECTED</t>
+          <t>LIBERTY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MER MONT</t>
+          <t>Adixon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mercure Paris Montmartre Sacré-Cœur</t>
+          <t>NOV MEG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Novotel Megève Mont-Blanc</t>
         </is>
       </c>
     </row>
@@ -561,12 +591,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Digitizme</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>NOV TE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Novotel Paris Centre Tour Eiffel</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Novotel Paris Tour Eiffel</t>
         </is>
       </c>
     </row>
